--- a/data/trans_orig/IP16A08-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A08-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>8282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23086</t>
+          <t>23102</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11600</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15447</t>
+          <t>15442</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>19184</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24986</t>
+          <t>26135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32872</t>
+          <t>33279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15154</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20904</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>15561</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14997</t>
+          <t>14985</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>22123</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29740</t>
+          <t>29906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,24%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>15012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>88,58%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>11941</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>10953</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>80,19%</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17128</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20243</t>
+          <t>20298</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25806</t>
+          <t>25810</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>39642</t>
+          <t>39398</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>46571</t>
+          <t>46566</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9097</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19825</t>
+          <t>19747</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30770</t>
+          <t>30951</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37818</t>
+          <t>37820</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>53653</t>
+          <t>53037</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>61882</t>
+          <t>61716</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31549</t>
+          <t>31017</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>32995</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>53489</t>
+          <t>52511</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>98446</t>
+          <t>98395</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>111893</t>
+          <t>112347</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>112370</t>
+          <t>112902</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>126882</t>
+          <t>127243</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>215735</t>
+          <t>216713</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>235077</t>
+          <t>236229</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,74%</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25365</t>
+          <t>25875</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32158</t>
+          <t>32240</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14794</t>
+          <t>14863</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21413</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19347</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24308</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36544</t>
+          <t>36324</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44539</t>
+          <t>44818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>12116</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16580</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31851</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37172</t>
+          <t>37165</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>464</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27253</t>
+          <t>26957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33409</t>
+          <t>33332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>9216</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20718</t>
+          <t>21040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>452</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9445</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19636</t>
+          <t>20192</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26547</t>
+          <t>26661</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11751</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25150</t>
+          <t>25141</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18612</t>
+          <t>18795</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24643</t>
+          <t>24653</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40153</t>
+          <t>40445</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48571</t>
+          <t>48944</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>12408</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>15721</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20586</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19296</t>
+          <t>19134</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30109</t>
+          <t>30506</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38592</t>
+          <t>39077</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>12225</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>25543</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>28961</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>47480</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>121864</t>
+          <t>121678</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>135252</t>
+          <t>134996</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>130533</t>
+          <t>129372</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>144644</t>
+          <t>143842</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>257766</t>
+          <t>257707</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>276651</t>
+          <t>276226</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>570</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15494</t>
+          <t>15511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>18636</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26221</t>
+          <t>26408</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33630</t>
+          <t>33782</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9053</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18210</t>
+          <t>17931</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24989</t>
+          <t>24936</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19267</t>
+          <t>19331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33613</t>
+          <t>33265</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42916</t>
+          <t>42876</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12218</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17181</t>
+          <t>17178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16938</t>
+          <t>16971</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23210</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>21379</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39303</t>
+          <t>40780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47604</t>
+          <t>47722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>769</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8685</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16189</t>
+          <t>15744</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17996</t>
+          <t>18107</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23620</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9077</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>16432</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>15935</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22231</t>
+          <t>22272</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33815</t>
+          <t>34301</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42295</t>
+          <t>42424</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25387</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25702</t>
+          <t>25464</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27028</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45709</t>
+          <t>45555</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>102074</t>
+          <t>102664</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>115485</t>
+          <t>115646</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>97574</t>
+          <t>97812</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>111374</t>
+          <t>111171</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>205028</t>
+          <t>205182</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>223709</t>
+          <t>223401</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25467</t>
+          <t>25778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45856</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52076</t>
+          <t>51970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>865</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9883</t>
+          <t>9640</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17619</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51332</t>
+          <t>50950</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61992</t>
+          <t>62189</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38280</t>
+          <t>38523</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46333</t>
+          <t>46153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93598</t>
+          <t>93999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107306</t>
+          <t>107247</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14963</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19645</t>
+          <t>19622</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32383</t>
+          <t>32270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37526</t>
+          <t>37520</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>8195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18841</t>
+          <t>19446</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>357</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10690</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20935</t>
+          <t>20930</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18524</t>
+          <t>19319</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26583</t>
+          <t>26892</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>34652</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43407</t>
+          <t>43049</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>57281</t>
+          <t>57492</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>68166</t>
+          <t>68526</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,43%</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11751</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18323</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27454</t>
+          <t>27497</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45449</t>
+          <t>45074</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>154592</t>
+          <t>155193</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>169939</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>154747</t>
+          <t>154704</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>170348</t>
+          <t>170310</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>314467</t>
+          <t>314842</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>337250</t>
+          <t>336088</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
